--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,36 +632,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,37 +689,33 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -895,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -953,22 +945,22 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1001,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1020,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1056,7 +1048,1339 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -776,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -815,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +923,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -965,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -998,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1042,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1161,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1298,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1331,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1355,33 +1391,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2277,22 +2317,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2325,12 +2365,12 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2344,7 +2384,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2369,7 +2409,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2380,7 +2420,1026 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1340,24 +1340,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1449,32 +1449,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1482,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,33 +1510,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1560,32 +1568,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1593,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1617,33 +1629,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1671,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1704,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1728,33 +1748,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1854,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1926,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1965,7 +1989,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2004,32 +2028,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2037,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2061,33 +2089,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2115,32 +2147,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2148,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2172,17 +2208,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2192,13 +2228,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2226,32 +2266,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2259,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2283,33 +2327,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2337,32 +2385,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -2370,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2394,33 +2446,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2861,7 +2917,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2933,7 +2989,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2987,7 +3043,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3104,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3087,7 +3143,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3102,7 +3158,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3176,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3163,7 +3219,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3177,7 +3233,7 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3274,7 +3330,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3323,7 +3379,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3389,7 +3445,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3443,6 +3499,1144 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,13 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,14 +1180,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>91.0</t>
@@ -1191,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1540,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1649,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,7 +1882,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1950,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2065,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2109,17 +2113,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2242,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2357,7 +2361,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2476,7 +2480,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2504,32 +2508,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2537,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2561,17 +2569,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2581,17 +2589,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2619,32 +2627,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2652,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2676,17 +2688,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2696,13 +2708,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2730,32 +2746,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2763,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2787,37 +2807,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2845,32 +2865,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2878,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2902,17 +2926,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2922,13 +2946,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2956,32 +2984,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2989,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3013,29 +3045,29 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>91.0</t>
@@ -3043,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3071,32 +3103,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3104,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3128,17 +3164,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3148,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3297,32 +3333,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3330,7 +3370,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3354,37 +3394,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3595,7 +3635,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3610,7 +3650,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3638,32 +3678,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3671,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3695,37 +3739,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3753,32 +3797,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3786,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3810,17 +3858,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3830,17 +3878,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3868,32 +3916,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3901,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3925,17 +3977,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3945,17 +3997,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4055,7 +4107,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4127,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4238,7 +4290,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4292,7 +4344,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4405,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4407,7 +4459,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4520,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4512,13 +4564,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4526,22 +4582,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4574,12 +4630,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4593,47 +4649,733 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>10/18</t>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,13 +1887,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,7 +1997,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2108,22 +2112,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2246,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2346,22 +2350,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2480,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2603,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,17 +2826,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2902,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,22 +2945,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,22 +3183,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3409,7 +3413,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3424,7 +3428,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3650,7 +3654,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3769,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3888,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3926,24 +3930,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3953,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3992,22 +3996,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4035,32 +4039,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -4068,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4092,17 +4100,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4112,13 +4120,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4218,7 +4230,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4257,32 +4269,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4290,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4314,37 +4330,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4421,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4459,7 +4475,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4487,32 +4503,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4520,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4544,37 +4564,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4602,32 +4622,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4635,7 +4659,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4659,32 +4683,32 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4717,32 +4741,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4750,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4774,37 +4802,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4919,7 +4947,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4980,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5019,7 +5047,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5034,7 +5062,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5095,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5149,7 +5177,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5238,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5264,7 +5292,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5272,22 +5300,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5325,7 +5353,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5339,43 +5367,848 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr"/>
-      <c r="AC42" s="2" t="inlineStr">
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,18 +1997,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,22 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2365,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2960,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3198,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3418,17 +3422,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3639,22 +3643,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3773,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3896,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3996,22 +4000,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,17 +4119,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4191,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4230,18 +4234,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4353,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4360,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4483,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4594,7 +4602,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4713,7 +4721,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4832,7 +4840,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4955,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4975,32 +4983,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5008,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5032,17 +5044,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5052,17 +5064,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5177,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5205,32 +5217,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5238,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5262,37 +5278,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5320,32 +5336,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5353,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5377,37 +5397,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5435,32 +5455,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5468,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5492,32 +5516,32 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5583,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5622,7 +5646,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5637,7 +5661,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5665,32 +5689,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5698,7 +5726,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5722,33 +5750,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5841,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5863,7 +5895,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5924,7 +5956,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5978,7 +6010,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6071,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6093,7 +6125,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6154,7 +6186,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6198,17 +6230,592 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB49" s="2" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>6/18</t>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,22 +2830,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,22 +3187,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,17 +3417,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,17 +4358,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4587,22 +4587,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4825,22 +4825,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5059,17 +5059,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5574,32 +5574,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5607,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5631,17 +5635,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5651,17 +5655,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5699,24 +5703,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5726,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5775,7 +5779,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5808,32 +5812,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5841,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5865,37 +5873,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5923,32 +5931,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5956,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5980,37 +5992,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6038,32 +6050,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6071,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6095,37 +6111,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6153,32 +6169,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6186,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6210,32 +6230,32 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6301,7 +6321,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6436,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6470,7 +6490,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6531,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6585,7 +6605,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6666,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6690,17 +6710,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6761,7 +6781,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6810,12 +6830,587 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1420,12 +1420,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,22 +2116,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3648,17 +3648,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,22 +4000,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5412,22 +5412,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,24 +6179,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6288,32 +6288,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6321,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6345,17 +6349,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6365,17 +6369,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6403,32 +6407,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6436,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6460,37 +6468,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6559,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6666,7 +6674,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6781,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6896,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,7 +7019,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7126,7 +7134,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7241,7 +7249,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7290,12 +7298,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7364,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7410,7 +7418,122 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,17 +4119,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5531,17 +5531,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,32 +6526,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6559,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6583,32 +6587,32 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6641,32 +6645,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6674,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6698,17 +6706,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6718,12 +6726,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6756,32 +6764,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6789,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6813,17 +6825,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6833,12 +6845,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6904,7 +6916,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7019,7 +7031,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7146,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,7 +7261,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,7 +7376,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7426,22 +7438,22 @@
       <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7474,12 +7486,12 @@
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7493,47 +7505,392 @@
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr">
         <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
           <t>14:45</t>
         </is>
       </c>
-      <c r="V60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W60" s="2" t="inlineStr">
+      <c r="W61" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X60" s="2" t="inlineStr">
+      <c r="X61" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y60" s="2" t="inlineStr">
+      <c r="Y61" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z60" s="2" t="inlineStr">
+      <c r="Z61" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
+      <c r="AA61" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
+      <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>85.8</t>
         </is>
       </c>
-      <c r="AC60" s="2" t="inlineStr">
+      <c r="AC61" s="2" t="inlineStr">
         <is>
           <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,22 +2830,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4353,22 +4353,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4587,12 +4587,12 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,17 +4830,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4868,12 +4868,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq21推进至seq34，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4909,10 +4909,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>张杨北路五莲路</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq16映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4940,7 +4952,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5020,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5064,12 +5076,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5135,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5189,7 +5201,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5266,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5373,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5427,7 +5439,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5504,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5611,7 +5623,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5650,22 +5662,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5769,7 +5781,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5849,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5888,12 +5900,12 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -5903,7 +5915,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6007,22 +6019,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6099,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6131,17 +6143,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,12 +6262,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6325,7 +6337,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6444,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6498,7 +6510,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6575,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6655,24 +6667,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6682,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6721,22 +6733,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6840,7 +6852,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6883,32 +6895,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6916,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6940,27 +6956,27 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -6970,7 +6986,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6998,32 +7014,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7031,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7055,37 +7075,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7113,32 +7133,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7146,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7170,17 +7194,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7190,17 +7214,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7228,32 +7252,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7261,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7285,17 +7313,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7305,12 +7333,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7376,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7491,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7660,7 +7688,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7749,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7836,7 +7864,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7894,6 +7922,1037 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>83.4</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,17 +2116,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,22 +2592,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3643,22 +3643,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3886,17 +3886,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,17 +4119,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程24%处后消失；随后反向物理轨迹由seq23推进至seq37，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5155,10 +5155,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="inlineStr"/>
-      <c r="R40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq11映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5186,7 +5198,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5266,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5305,22 +5317,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5424,17 +5436,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5504,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5543,17 +5555,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5623,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5662,7 +5674,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5677,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5861,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5980,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6099,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6138,7 +6150,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6218,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6257,7 +6269,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6337,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6376,22 +6388,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6495,17 +6507,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6575,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6614,17 +6626,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6694,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6733,7 +6745,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6748,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6932,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7051,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7170,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7209,7 +7221,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7289,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7328,7 +7340,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7371,32 +7383,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7404,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7428,37 +7444,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7486,32 +7502,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7519,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7543,37 +7563,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7601,32 +7621,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7634,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7658,32 +7682,32 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7716,32 +7740,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7749,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7773,32 +7801,32 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7831,32 +7859,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7864,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7888,37 +7920,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7979,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8018,7 +8050,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8090,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8129,7 +8161,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8144,7 +8176,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8172,32 +8204,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8205,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8229,17 +8265,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8249,17 +8285,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8320,7 +8356,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8374,7 +8410,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8435,7 +8471,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8550,7 +8586,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8604,7 +8640,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8665,7 +8701,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8719,7 +8755,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8816,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8895,7 +8931,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8953,6 +8989,1152 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>84.6</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,14 +1648,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>96.3</t>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,17 +1997,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,22 +2473,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,22 +2711,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,17 +2830,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2949,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,14 +3881,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>96.3</t>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4234,17 +4234,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4468,22 +4468,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4587,22 +4587,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,17 +4830,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5071,22 +5071,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,22 +5198,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,17 +5793,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,22 +5912,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,17 +6155,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6864,17 +6864,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,22 +6983,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7102,17 +7102,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7226,17 +7226,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,22 +7340,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8089,32 +8089,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8122,7 +8126,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8146,17 +8150,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8166,7 +8170,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8241,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8280,14 +8284,14 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>96.3</t>
@@ -8295,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8323,32 +8327,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -8356,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8380,37 +8388,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8438,32 +8446,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8471,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8495,32 +8507,32 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8586,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8625,7 +8637,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8640,7 +8652,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8668,32 +8680,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8701,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8725,37 +8741,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8783,32 +8799,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8816,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8840,37 +8860,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8898,32 +8918,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8931,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8955,32 +8979,32 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9013,32 +9037,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9046,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9070,37 +9098,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9128,32 +9156,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9161,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9185,17 +9217,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9205,17 +9237,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9243,32 +9275,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9276,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9300,37 +9336,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9445,7 +9481,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9560,7 +9596,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9621,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9736,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9790,7 +9826,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9966,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10010,7 +10046,7 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
@@ -10081,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10135,6 +10171,1041 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>96.3</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>84.6</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,18 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1420,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2250,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2553,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2711,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2964,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3072,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3148,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,22 +3191,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3427,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3532,18 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3648,17 +3656,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3723,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3777,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3886,17 +3894,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,22 +4008,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4119,22 +4127,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4314,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,17 +4366,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4548,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4602,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4721,7 +4729,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4825,22 +4833,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4952,7 +4960,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5032,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5081,12 +5089,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5213,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,22 +5444,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,22 +5563,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,17 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5873,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5992,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6046,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,22 +6158,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6279,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,22 +6515,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,22 +6634,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,17 +6758,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6944,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6998,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7117,7 +7125,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7221,22 +7229,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7350,12 +7358,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,22 +7467,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,17 +7591,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7697,22 +7705,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7816,22 +7824,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7935,7 +7943,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7950,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8050,18 +8058,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8170,17 +8182,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8289,17 +8301,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8403,22 +8415,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8598,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8637,7 +8649,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8717,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8836,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8890,7 +8902,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9009,7 +9021,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9128,7 +9140,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9166,24 +9178,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9193,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9232,22 +9244,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9285,24 +9297,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9312,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9361,12 +9373,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9394,32 +9406,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9427,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9451,37 +9467,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9509,32 +9525,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9542,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9566,37 +9586,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9624,32 +9644,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9657,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9681,17 +9705,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9701,17 +9725,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9811,7 +9835,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9826,7 +9850,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9854,32 +9878,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9887,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9911,37 +9939,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9969,32 +9997,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10002,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10026,17 +10058,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10046,17 +10078,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10084,32 +10116,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10117,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10141,33 +10177,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB82" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10195,32 +10235,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10228,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10252,17 +10296,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10272,17 +10316,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10310,32 +10354,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10343,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10367,37 +10415,37 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA84" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10458,7 +10506,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10573,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10688,7 +10736,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10727,7 +10775,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10803,7 +10851,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10857,7 +10905,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10966,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10972,7 +11020,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11033,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11082,12 +11130,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11196,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11202,7 +11250,927 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
           <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>83.6</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,12 +2006,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,12 +4247,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4600,17 +4600,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,17 +4719,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,17 +6044,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6996,17 +6996,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7115,17 +7115,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,12 +8654,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8892,17 +8892,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9125,7 +9125,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9368,12 +9368,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10019,12 +10019,12 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10257,12 +10257,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10364,24 +10364,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>18:49</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10473,32 +10473,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10506,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10530,17 +10534,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10550,12 +10554,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10621,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10660,7 +10664,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10703,32 +10707,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10736,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10760,17 +10768,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10780,12 +10788,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10818,32 +10826,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10851,7 +10863,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10875,17 +10887,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10895,17 +10907,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10933,32 +10945,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10966,7 +10982,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10990,17 +11006,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11010,17 +11026,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11048,32 +11064,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11081,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11105,17 +11125,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11125,12 +11145,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11196,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11235,7 +11255,7 @@
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11250,7 +11270,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11311,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11365,7 +11385,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11480,7 +11500,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11541,7 +11561,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11580,7 +11600,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11595,7 +11615,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11656,7 +11676,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11710,7 +11730,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11771,7 +11791,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11825,7 +11845,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11906,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11935,12 +11955,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12001,7 +12021,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12055,7 +12075,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12136,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12160,17 +12180,477 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>98.2</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
-        <is>
-          <t>15/18</t>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4013,12 +4013,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5449,12 +5449,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9130,17 +9130,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11183,32 +11183,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11216,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11240,17 +11244,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11260,17 +11264,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11413,32 +11417,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11446,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11470,17 +11478,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11490,12 +11498,12 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11561,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11676,7 +11684,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11791,7 +11799,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11906,7 +11914,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12021,7 +12029,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12136,7 +12144,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12251,7 +12259,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12366,7 +12374,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12410,17 +12418,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12489,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12596,7 +12604,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,17 +1652,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,17 +3077,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,22 +3536,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3889,17 +3889,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6287,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7472,17 +7472,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8058,22 +8058,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8296,17 +8296,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8420,17 +8420,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,17 +8654,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9205,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9373,12 +9373,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9487,17 +9487,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9959,12 +9959,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10192,22 +10192,22 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10435,17 +10435,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10788,17 +10788,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11074,24 +11074,24 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11150,12 +11150,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11302,32 +11302,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11335,7 +11339,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11359,17 +11363,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11379,12 +11383,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11454,7 +11458,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11508,7 +11512,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11536,32 +11540,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11569,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11593,17 +11601,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11613,17 +11621,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11684,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11738,7 +11746,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11766,32 +11774,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11799,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11823,17 +11835,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11843,12 +11855,12 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11881,32 +11893,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11914,7 +11930,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11938,17 +11954,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11958,17 +11974,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11996,32 +12012,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12029,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12053,37 +12073,37 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12111,32 +12131,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12144,7 +12168,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12168,17 +12192,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12188,17 +12212,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12226,32 +12250,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12259,7 +12287,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12283,32 +12311,32 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA100" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12374,7 +12402,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12428,7 +12456,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12517,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12528,7 +12556,7 @@
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
@@ -12543,7 +12571,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12604,7 +12632,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12648,17 +12676,362 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>95.2</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7125,7 +7125,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,17 +8063,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8773,17 +8773,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9130,17 +9130,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9735,7 +9735,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10197,17 +10197,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10669,17 +10669,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11264,17 +11264,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11512,7 +11512,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11984,7 +11984,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12093,17 +12093,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12369,32 +12369,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12402,7 +12406,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12426,17 +12430,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12446,17 +12450,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12484,32 +12488,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12517,7 +12525,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12541,17 +12549,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12561,17 +12569,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -12599,32 +12607,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12632,7 +12644,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12656,17 +12668,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12676,12 +12688,12 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
@@ -12714,32 +12726,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12747,7 +12763,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12771,17 +12787,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12791,17 +12807,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -12862,7 +12878,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12977,7 +12993,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13021,17 +13037,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-浦东78路.xlsx
+++ b/data/export/2026-10-15-浦东78路.xlsx
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3894,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8301,17 +8301,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10316,17 +10316,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12098,7 +12098,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12287,7 +12287,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12331,17 +12331,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12736,12 +12736,12 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
@@ -12763,7 +12763,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
@@ -12845,32 +12845,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12878,7 +12882,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12902,17 +12906,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12922,17 +12926,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12993,7 +12997,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
